--- a/examples/PRTG-Export-Demo.xlsx
+++ b/examples/PRTG-Export-Demo.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sensoren" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Hinweise" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,14 +418,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -547,7 +548,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SNMP Traffic</t>
+          <t>SNMP Traffic GigabitEthernet0/0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -569,17 +570,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sw-core-01</t>
+          <t>fw-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>192.0.2.2</t>
+          <t>192.0.2.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ping</t>
+          <t>CPU Load</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -611,7 +612,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SNMP Traffic</t>
+          <t>Ping</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -633,17 +634,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sw-access-01</t>
+          <t>sw-core-01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>192.0.2.3</t>
+          <t>192.0.2.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ping</t>
+          <t>SNMP Traffic GigabitEthernet1/0/1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -665,22 +666,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sw-access-01</t>
+          <t>sw-core-01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>192.0.2.3</t>
+          <t>192.0.2.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SNMP Traffic</t>
+          <t>SNMP Traffic GigabitEthernet1/0/2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Up</t>
         </is>
       </c>
     </row>
@@ -692,22 +693,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Site B Servers</t>
+          <t>Site A Network</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>srv-dc-01</t>
+          <t>sw-core-01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>198.51.100.10</t>
+          <t>192.0.2.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ping</t>
+          <t>SNMP Uptime</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -724,22 +725,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Site B Servers</t>
+          <t>Site A Network</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>srv-dc-01</t>
+          <t>sw-access-01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>198.51.100.10</t>
+          <t>192.0.2.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DNS</t>
+          <t>Ping</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -756,27 +757,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Site B Servers</t>
+          <t>Site A Network</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>srv-dc-01</t>
+          <t>sw-access-01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>198.51.100.10</t>
+          <t>192.0.2.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CPU Load</t>
+          <t>SNMP Traffic GigabitEthernet0/1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Warning</t>
         </is>
       </c>
     </row>
@@ -788,22 +789,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Site B Servers</t>
+          <t>Site A Network</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>srv-dc-01</t>
+          <t>sw-access-01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>198.51.100.10</t>
+          <t>192.0.2.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Memory</t>
+          <t>SNMP Uptime</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -825,12 +826,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>srv-app-01</t>
+          <t>srv-dc-01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>198.51.100.11</t>
+          <t>198.51.100.10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -857,17 +858,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>srv-app-01</t>
+          <t>srv-dc-01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>198.51.100.11</t>
+          <t>198.51.100.10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>DNS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -889,12 +890,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>srv-app-01</t>
+          <t>srv-dc-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>198.51.100.11</t>
+          <t>198.51.100.10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -921,17 +922,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>srv-app-01</t>
+          <t>srv-dc-01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>198.51.100.11</t>
+          <t>198.51.100.10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Disk Free</t>
+          <t>Memory</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -953,17 +954,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>srv-db-01</t>
+          <t>srv-dc-01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>198.51.100.12</t>
+          <t>198.51.100.10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ping</t>
+          <t>Disk Free C:\</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -985,17 +986,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>srv-db-01</t>
+          <t>srv-app-01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>198.51.100.12</t>
+          <t>198.51.100.11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ping</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1017,22 +1018,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>srv-db-01</t>
+          <t>srv-app-01</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>198.51.100.12</t>
+          <t>198.51.100.11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CPU Load</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Up</t>
         </is>
       </c>
     </row>
@@ -1049,17 +1050,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>srv-db-01</t>
+          <t>srv-app-01</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>198.51.100.12</t>
+          <t>198.51.100.11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Disk Free</t>
+          <t>CPU Load</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1076,22 +1077,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Site C Branch</t>
+          <t>Site B Servers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rtr-branch-01</t>
+          <t>srv-app-01</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>203.0.113.1</t>
+          <t>198.51.100.11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ping</t>
+          <t>Disk Free C:\</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1108,22 +1109,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Site C Branch</t>
+          <t>Site B Servers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>rtr-branch-01</t>
+          <t>srv-app-01</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>203.0.113.1</t>
+          <t>198.51.100.11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SNMP Traffic</t>
+          <t>Disk Free D:\</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1140,17 +1141,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Site C Branch</t>
+          <t>Site B Servers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nas-branch-01</t>
+          <t>srv-db-01</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>203.0.113.5</t>
+          <t>198.51.100.12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1160,7 +1161,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
     </row>
@@ -1172,27 +1173,435 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>Site B Servers</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>srv-db-01</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>198.51.100.12</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Port 1433</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Demo Probe</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Site B Servers</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>srv-db-01</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>198.51.100.12</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>CPU Load</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Demo Probe</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Site B Servers</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>srv-db-01</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>198.51.100.12</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Disk Free C:\</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Demo Probe</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Site B Servers</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>srv-db-01</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>198.51.100.12</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Disk Free E:\</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Demo Probe</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>Site C Branch</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>rtr-branch-01</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>203.0.113.1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ping v2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Demo Probe</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Site C Branch</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>rtr-branch-01</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>203.0.113.1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SNMP Traffic Dialer1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Demo Probe</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Site C Branch</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>rtr-branch-01</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>203.0.113.1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SNMP Uptime</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Demo Probe</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Site C Branch</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>nas-branch-01</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>203.0.113.5</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Disk Free</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ping</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Down</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Demo Probe</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Site C Branch</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>nas-branch-01</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>203.0.113.5</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Disk Free /volume1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Demo Probe</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Site C Branch</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>nas-branch-01</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>203.0.113.5</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SNMP Traffic eth0</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="100" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Demo data, not a real network.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>All addresses come from the RFC 5737 documentation ranges (192.0.2.0/24, 198.51.100.0/24,</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>203.0.113.0/24), so they cannot collide with anyone’s real network.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>The sheet imitates what a PRTG sensor export actually looks like, including the part that</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>makes a migration awkward: many sensor names carry their parameters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  "Ping", "HTTP", "CPU Load"            - the display name IS the sensor type, these import</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  "Ping v2"                             - the API v2 type, kind paessler.icmp.ping_sensor</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  "SNMP Traffic GigabitEthernet0/0"     - type plus interface; the interface cannot be derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  "Disk Free C:\", "Port 1433"          - type plus drive or port, same problem</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>The import script resolves sensor types by display name. Rows whose name carries parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>are reported and skipped rather than created with some arbitrary default interface or drive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>They have to be recreated in PRTG, or through a discovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Worksheet name "Sensoren" is deliberate: that is what a German PRTG installation exports.</t>
         </is>
       </c>
     </row>
